--- a/reports/一级子公司A_利润表_2025-05.xlsx
+++ b/reports/一级子公司A_利润表_2025-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>176208429</v>
+        <v>180326128</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>171688653</v>
+        <v>171903397</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>799492796</v>
+        <v>798126222</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>698032</v>
+        <v>702799</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3253181</v>
+        <v>3262727</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>607907</v>
+        <v>608612</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2823060</v>
+        <v>2832158</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>514049</v>
+        <v>514652</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2390308</v>
+        <v>2400323</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>475702</v>
+        <v>472505</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2201472</v>
+        <v>2207646</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>257620</v>
+        <v>256372</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1195758</v>
+        <v>1199020</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>207157</v>
+        <v>204925</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>958091</v>
+        <v>958383</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>173447962</v>
+        <v>177566263</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>168928186</v>
+        <v>169143532</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>87288084</v>
+        <v>86661053</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>405582995</v>
+        <v>404076629</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1596803</v>
+        <v>1594435</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>7438448</v>
+        <v>7407748</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1442644</v>
+        <v>1444954</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6717329</v>
+        <v>6692168</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>76876539</v>
+        <v>77695598</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>358923579</v>
+        <v>359062608</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1652860</v>
+        <v>1656994</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>7673063</v>
+        <v>7664223</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>716677</v>
+        <v>724689</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3350546</v>
+        <v>3354826</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2583615</v>
+        <v>2583727</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>11984079</v>
+        <v>11997118</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1128234</v>
+        <v>1136382</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5261205</v>
+        <v>5278650</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4429780</v>
+        <v>4434070</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>20573677</v>
+        <v>20641897</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89996</v>
+        <v>89891</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>449329</v>
+        <v>450982</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2340555</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>10940082</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1558215</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7288085</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>117668078</v>
+        <v>125725601</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>105128841</v>
+        <v>104786002</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>102957050</v>
+        <v>102627353</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>479090793</v>
+        <v>478228235</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2171791</v>
+        <v>2158649</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>10077233</v>
+        <v>10038268</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3915670</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18161577</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1255664</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5813248</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>786097</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3635499</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>944187</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4366294</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>708157</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3277782</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>471689</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2187062</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>392433</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1823700</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1795949</v>
+        <v>1803343</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8366735</v>
+        <v>8401082</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1395205</v>
+        <v>1388134</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6462081</v>
+        <v>6480149</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1132422</v>
+        <v>1129051</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5260251</v>
+        <v>5277849</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8587935</v>
+        <v>8507897</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>39743925</v>
+        <v>39793694</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>350867</v>
+        <v>358597</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1749037</v>
+        <v>1676635</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>672064</v>
+        <v>666814</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3350865</v>
+        <v>3347678</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>762463</v>
+        <v>666814</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3803396</v>
+        <v>3347678</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>89980</v>
+        <v>89852</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>450392</v>
+        <v>449108</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>342247</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1706253</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>686867</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3179322</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>228999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1138371</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>171888</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>854466</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>286452</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1425417</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>982509</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4556834</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152362</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>761383</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114028</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>571230</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>189632</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>952015</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>132498</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>666137</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>94529</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>475473</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>75601</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>380040</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56736</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>284773</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>55779884</v>
+        <v>54232293</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>64665927</v>
+        <v>60642809</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>391796</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1816218</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>95289</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>474082</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>149444</v>
+        <v>150678</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>750546</v>
+        <v>748989</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>55630440</v>
+        <v>54473411</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5269917</v>
+        <v>5326580</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>26485058</v>
+        <v>26510872</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50360523</v>
+        <v>49146831</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50360523</v>
+        <v>49146831</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50360523</v>
+        <v>49146831</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50360523</v>
+        <v>49146831</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50360523</v>
+        <v>49146831</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
